--- a/AAAGameData/Languages/Korean.xlsx
+++ b/AAAGameData/Languages/Korean.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>BRAKE</t>
   </si>
@@ -72,10 +72,13 @@
     <t>Failed</t>
   </si>
   <si>
-    <t/>
+    <t>게임 실패</t>
   </si>
   <si>
     <t>GameOverUIForm.Back</t>
+  </si>
+  <si>
+    <t>돌아가다</t>
   </si>
   <si>
     <t>Level.DisplayName1</t>
@@ -232,6 +235,9 @@
   </si>
   <si>
     <t>Victory</t>
+  </si>
+  <si>
+    <t>게임 승리</t>
   </si>
 </sst>
 </file>
@@ -2153,6 +2159,502 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -4864,250 +5366,250 @@
         <v>6</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1"/>
       <c r="B10" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1"/>
       <c r="B11" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
       <c r="B12" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1"/>
       <c r="B13" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1"/>
       <c r="B14" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1"/>
       <c r="B15" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1"/>
       <c r="B16" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1"/>
       <c r="B17" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1"/>
       <c r="B18" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1"/>
       <c r="B19" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1"/>
       <c r="B20" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1"/>
       <c r="B21" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1"/>
       <c r="B22" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1"/>
       <c r="B23" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1"/>
       <c r="B24" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1"/>
       <c r="B25" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1"/>
       <c r="B29" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -5119,7 +5621,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId421" name="A1">
+            <control shapeId="1056" r:id="rId541" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5141,7 +5643,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId422" name="A2">
+            <control shapeId="1057" r:id="rId542" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5163,7 +5665,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId423" name="A3">
+            <control shapeId="1058" r:id="rId543" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5185,7 +5687,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId424" name="A4">
+            <control shapeId="1059" r:id="rId544" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5207,7 +5709,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId425" name="A5">
+            <control shapeId="1060" r:id="rId545" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5229,7 +5731,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId426" name="A6">
+            <control shapeId="1061" r:id="rId546" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5251,7 +5753,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId427" name="A7">
+            <control shapeId="1062" r:id="rId547" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5273,7 +5775,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId428" name="A8">
+            <control shapeId="1063" r:id="rId548" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5295,7 +5797,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId429" name="A9">
+            <control shapeId="1064" r:id="rId549" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5317,7 +5819,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId430" name="A10">
+            <control shapeId="1065" r:id="rId550" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5339,7 +5841,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId431" name="A11">
+            <control shapeId="1066" r:id="rId551" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5361,7 +5863,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId432" name="A12">
+            <control shapeId="1067" r:id="rId552" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5383,7 +5885,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId433" name="A13">
+            <control shapeId="1068" r:id="rId553" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5405,7 +5907,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId434" name="A14">
+            <control shapeId="1069" r:id="rId554" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5427,7 +5929,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId435" name="A15">
+            <control shapeId="1070" r:id="rId555" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5449,7 +5951,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId436" name="A16">
+            <control shapeId="1071" r:id="rId556" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5471,7 +5973,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId437" name="A17">
+            <control shapeId="1072" r:id="rId557" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5493,7 +5995,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId438" name="A18">
+            <control shapeId="1073" r:id="rId558" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5515,7 +6017,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId439" name="A19">
+            <control shapeId="1074" r:id="rId559" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5537,7 +6039,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId440" name="A20">
+            <control shapeId="1075" r:id="rId560" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5559,7 +6061,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId441" name="A21">
+            <control shapeId="1076" r:id="rId561" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5581,7 +6083,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId442" name="A22">
+            <control shapeId="1077" r:id="rId562" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5603,7 +6105,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId443" name="A23">
+            <control shapeId="1078" r:id="rId563" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5625,7 +6127,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId444" name="A24">
+            <control shapeId="1079" r:id="rId564" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5647,7 +6149,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId445" name="A25">
+            <control shapeId="1080" r:id="rId565" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5669,7 +6171,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId446" name="A26">
+            <control shapeId="1081" r:id="rId566" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5691,7 +6193,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId447" name="A27">
+            <control shapeId="1082" r:id="rId567" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5713,7 +6215,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId448" name="A28">
+            <control shapeId="1083" r:id="rId568" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5735,7 +6237,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId449" name="A29">
+            <control shapeId="1084" r:id="rId569" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5757,7 +6259,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId450" name="A30">
+            <control shapeId="1085" r:id="rId570" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5779,7 +6281,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId451" name="A31">
+            <control shapeId="1086" r:id="rId571" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>

--- a/AAAGameData/Languages/Korean.xlsx
+++ b/AAAGameData/Languages/Korean.xlsx
@@ -55,66 +55,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
-    <t>BRAKE</t>
+    <t>NoSaveData</t>
   </si>
   <si>
-    <t>중단</t>
-  </si>
-  <si>
-    <t>ENGINE</t>
-  </si>
-  <si>
-    <t>엔진</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>게임 실패</t>
-  </si>
-  <si>
-    <t>GameOverUIForm.Back</t>
-  </si>
-  <si>
-    <t>돌아가다</t>
-  </si>
-  <si>
-    <t>Level.DisplayName1</t>
-  </si>
-  <si>
-    <t>관문 1 이름</t>
-  </si>
-  <si>
-    <t>Level.DisplayName2</t>
-  </si>
-  <si>
-    <t>관문 2 이름</t>
-  </si>
-  <si>
-    <t>Level.DisplayName3</t>
-  </si>
-  <si>
-    <t>관문 3 이름</t>
-  </si>
-  <si>
-    <t>Level.DisplayName4</t>
-  </si>
-  <si>
-    <t>관문 4 이름</t>
-  </si>
-  <si>
-    <t>Level.DisplayName5</t>
-  </si>
-  <si>
-    <t>관문 5 이름</t>
-  </si>
-  <si>
-    <t>MenuUIForm.Tips</t>
-  </si>
-  <si>
-    <t>시작 클릭</t>
+    <t/>
   </si>
   <si>
     <t>Nothing</t>
@@ -126,43 +72,19 @@
     <t>OFF</t>
   </si>
   <si>
-    <t>끄기</t>
+    <t>관</t>
   </si>
   <si>
     <t>ON</t>
   </si>
   <si>
-    <t>켜기</t>
+    <t>열다</t>
   </si>
   <si>
-    <t>RatingDialog.CancelTxt</t>
+    <t>OpenSaveList</t>
   </si>
   <si>
-    <t>취소</t>
-  </si>
-  <si>
-    <t>RatingDialog.Description</t>
-  </si>
-  <si>
-    <t>이 게임 좋아해요?\n 별 다섯 개 호평해 주세요!</t>
-  </si>
-  <si>
-    <t>RatingDialog.HighRatingTips</t>
-  </si>
-  <si>
-    <t>당신의 긍정에 감사 드립니다!우리는 더욱 분발할 것이다!</t>
-  </si>
-  <si>
-    <t>RatingDialog.LowRatingTips</t>
-  </si>
-  <si>
-    <t>당신의 평가에 감사드립니다. 우리는 최선을 다해 최적화를 완비합니다!</t>
-  </si>
-  <si>
-    <t>RatingDialog.RateTxt</t>
-  </si>
-  <si>
-    <t>별을 평가하다</t>
+    <t>저장 목록 열기</t>
   </si>
   <si>
     <t>Settings.Help</t>
@@ -192,7 +114,7 @@
     <t>Settings.Rating</t>
   </si>
   <si>
-    <t>채점</t>
+    <t>평점</t>
   </si>
   <si>
     <t>Settings.SFX</t>
@@ -204,7 +126,7 @@
     <t>Settings.Title</t>
   </si>
   <si>
-    <t>설치</t>
+    <t>설정</t>
   </si>
   <si>
     <t>Settings.Vibrate</t>
@@ -213,13 +135,10 @@
     <t>진동</t>
   </si>
   <si>
-    <t>SHOP</t>
+    <t>Story_Welcome</t>
   </si>
   <si>
-    <t>상점</t>
-  </si>
-  <si>
-    <t>STEERING</t>
+    <t>신들의 전쟁의 세계에 오신 것을 환영합니다.여기서 당신은 영웅 역을 맡아 서사시 같은 모험의 여정에 오를 것이다.당신의 전설을 시작할 준비가 되셨나요?</t>
   </si>
   <si>
     <t>TermsOfService</t>
@@ -228,16 +147,28 @@
     <t>서비스 약관</t>
   </si>
   <si>
-    <t>UNLOCK</t>
+    <t>UI_Continue</t>
   </si>
   <si>
-    <t>잠금 해제</t>
+    <t>계속</t>
   </si>
   <si>
-    <t>Victory</t>
+    <t>UI_InputName</t>
   </si>
   <si>
-    <t>게임 승리</t>
+    <t>이름을 입력하세요</t>
+  </si>
+  <si>
+    <t>UI_PressSpace</t>
+  </si>
+  <si>
+    <t>스페이스바를 눌러 계속합니다.</t>
+  </si>
+  <si>
+    <t>UI_Welcome</t>
+  </si>
+  <si>
+    <t>환영합니다, {0}!</t>
   </si>
 </sst>
 </file>
@@ -305,7 +236,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -313,7 +244,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
@@ -321,7 +252,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
@@ -332,55 +263,7 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -2655,6 +2538,794 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -2671,7 +3342,1039 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1056">
+            <xdr:cNvPr hidden="1" name="A1" id="1044">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1044"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A2" id="1045">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1045"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A3" id="1046">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1046"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A4" id="1047">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1047"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A5" id="1048">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1048"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A6" id="1049">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1049"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A7" id="1050">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1050"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A8" id="1051">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1051"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A9" id="1052">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1052"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A10" id="1053">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1053"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A11" id="1054">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1054"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A12" id="1055">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1055"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A13" id="1056">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1056"/>
@@ -2746,18 +4449,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1057">
+            <xdr:cNvPr hidden="1" name="A14" id="1057">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1057"/>
@@ -2832,18 +4535,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1058">
+            <xdr:cNvPr hidden="1" name="A15" id="1058">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1058"/>
@@ -2918,18 +4621,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1059">
+            <xdr:cNvPr hidden="1" name="A16" id="1059">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1059"/>
@@ -3004,18 +4707,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1060">
+            <xdr:cNvPr hidden="1" name="A17" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1060"/>
@@ -3090,18 +4793,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1061">
+            <xdr:cNvPr hidden="1" name="A18" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -3176,18 +4879,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1062">
+            <xdr:cNvPr hidden="1" name="A19" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1062"/>
@@ -3256,2080 +4959,16 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1063">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1063"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1064">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1064"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1065">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1065"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1066">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1066"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1067">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1067"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1068">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1068"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1069">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1069"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1070">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1070"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1071">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1071"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1072">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1072"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1073">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1073"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1074">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1074"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1075">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1075"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1076">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1076"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1077">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1077"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1078">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1078"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1079">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1079"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1080">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1080"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1081">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1081"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1082">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1082"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1083">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1083"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1084">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1084"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1085">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1085"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1086">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1086"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="25.4074859619141" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5504,114 +5143,6 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1"/>
-      <c r="B20" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1"/>
-      <c r="B21" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1"/>
-      <c r="B22" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1"/>
-      <c r="B23" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1"/>
-      <c r="B24" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1"/>
-      <c r="B26" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1"/>
-      <c r="B27" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1"/>
-      <c r="B28" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1"/>
-      <c r="B29" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1"/>
-      <c r="B30" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1"/>
-      <c r="B31" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>60</v>
-      </c>
-    </row>
   </sheetData>
   <headerFooter/>
   <drawing r:id="rId1"/>
@@ -5621,7 +5152,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId541" name="A1">
+            <control shapeId="1044" r:id="rId727" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5643,7 +5174,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId542" name="A2">
+            <control shapeId="1045" r:id="rId728" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5665,7 +5196,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId543" name="A3">
+            <control shapeId="1046" r:id="rId729" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5687,7 +5218,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId544" name="A4">
+            <control shapeId="1047" r:id="rId730" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5709,7 +5240,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId545" name="A5">
+            <control shapeId="1048" r:id="rId731" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5731,7 +5262,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId546" name="A6">
+            <control shapeId="1049" r:id="rId732" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5753,7 +5284,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId547" name="A7">
+            <control shapeId="1050" r:id="rId733" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5775,7 +5306,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId548" name="A8">
+            <control shapeId="1051" r:id="rId734" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5797,7 +5328,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId549" name="A9">
+            <control shapeId="1052" r:id="rId735" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5819,7 +5350,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId550" name="A10">
+            <control shapeId="1053" r:id="rId736" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5841,7 +5372,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId551" name="A11">
+            <control shapeId="1054" r:id="rId737" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5863,7 +5394,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId552" name="A12">
+            <control shapeId="1055" r:id="rId738" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5885,7 +5416,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId553" name="A13">
+            <control shapeId="1056" r:id="rId739" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5907,7 +5438,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId554" name="A14">
+            <control shapeId="1057" r:id="rId740" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5929,7 +5460,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId555" name="A15">
+            <control shapeId="1058" r:id="rId741" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5951,7 +5482,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId556" name="A16">
+            <control shapeId="1059" r:id="rId742" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5973,7 +5504,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId557" name="A17">
+            <control shapeId="1060" r:id="rId743" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5995,7 +5526,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId558" name="A18">
+            <control shapeId="1061" r:id="rId744" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6017,7 +5548,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId559" name="A19">
+            <control shapeId="1062" r:id="rId745" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6037,270 +5568,6 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId560" name="A20">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>19</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>20</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId561" name="A21">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>20</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>21</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId562" name="A22">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>21</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>22</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId563" name="A23">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>22</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>23</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId564" name="A24">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>23</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>24</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId565" name="A25">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>24</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>25</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId566" name="A26">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>25</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>26</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId567" name="A27">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>26</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>27</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId568" name="A28">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>27</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>28</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId569" name="A29">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>28</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>29</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId570" name="A30">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>29</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>30</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId571" name="A31">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>30</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>31</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Korean.xlsx
+++ b/AAAGameData/Languages/Korean.xlsx
@@ -55,12 +55,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>NoSaveData</t>
   </si>
   <si>
-    <t/>
+    <t>아카이브 데이터 없음</t>
   </si>
   <si>
     <t>Nothing</t>
@@ -87,6 +87,30 @@
     <t>저장 목록 열기</t>
   </si>
   <si>
+    <t>scene.base.name</t>
+  </si>
+  <si>
+    <t>기지</t>
+  </si>
+  <si>
+    <t>scene.menu.name</t>
+  </si>
+  <si>
+    <t>메인 메뉴</t>
+  </si>
+  <si>
+    <t>scene.tutorial.name</t>
+  </si>
+  <si>
+    <t>어느 실험실</t>
+  </si>
+  <si>
+    <t>scene.world.name</t>
+  </si>
+  <si>
+    <t>대세계</t>
+  </si>
+  <si>
     <t>Settings.Help</t>
   </si>
   <si>
@@ -102,25 +126,25 @@
     <t>Settings.Music</t>
   </si>
   <si>
-    <t>배경음악</t>
+    <t>배경 음악</t>
   </si>
   <si>
     <t>Settings.Privacy</t>
   </si>
   <si>
-    <t>개인 정보 보호 프로토콜</t>
+    <t>개인정보 처리방침</t>
   </si>
   <si>
     <t>Settings.Rating</t>
   </si>
   <si>
-    <t>평점</t>
+    <t>채점</t>
   </si>
   <si>
     <t>Settings.SFX</t>
   </si>
   <si>
-    <t>음향 효과</t>
+    <t>사운드 효과</t>
   </si>
   <si>
     <t>Settings.Title</t>
@@ -168,7 +192,7 @@
     <t>UI_Welcome</t>
   </si>
   <si>
-    <t>환영합니다, {0}!</t>
+    <t>환영합니다</t>
   </si>
 </sst>
 </file>
@@ -236,7 +260,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -244,7 +268,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
@@ -260,6 +284,22 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -3326,6 +3366,634 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -3342,351 +4010,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1044">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1044"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1045">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1045"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1046">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1046"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1047">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1047"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1048">
+            <xdr:cNvPr hidden="1" name="A1" id="1048">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1048"/>
@@ -3761,18 +4085,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1049">
+            <xdr:cNvPr hidden="1" name="A2" id="1049">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1049"/>
@@ -3847,18 +4171,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1050">
+            <xdr:cNvPr hidden="1" name="A3" id="1050">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1050"/>
@@ -3933,18 +4257,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1051">
+            <xdr:cNvPr hidden="1" name="A4" id="1051">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1051"/>
@@ -4019,18 +4343,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1052">
+            <xdr:cNvPr hidden="1" name="A5" id="1052">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1052"/>
@@ -4105,18 +4429,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1053">
+            <xdr:cNvPr hidden="1" name="A6" id="1053">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1053"/>
@@ -4191,18 +4515,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1054">
+            <xdr:cNvPr hidden="1" name="A7" id="1054">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1054"/>
@@ -4277,18 +4601,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1055">
+            <xdr:cNvPr hidden="1" name="A8" id="1055">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1055"/>
@@ -4363,18 +4687,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1056">
+            <xdr:cNvPr hidden="1" name="A9" id="1056">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1056"/>
@@ -4449,18 +4773,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1057">
+            <xdr:cNvPr hidden="1" name="A10" id="1057">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1057"/>
@@ -4535,18 +4859,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1058">
+            <xdr:cNvPr hidden="1" name="A11" id="1058">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1058"/>
@@ -4621,18 +4945,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1059">
+            <xdr:cNvPr hidden="1" name="A12" id="1059">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1059"/>
@@ -4707,18 +5031,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1060">
+            <xdr:cNvPr hidden="1" name="A13" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1060"/>
@@ -4793,18 +5117,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1061">
+            <xdr:cNvPr hidden="1" name="A14" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -4879,18 +5203,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1062">
+            <xdr:cNvPr hidden="1" name="A15" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1062"/>
@@ -4959,12 +5283,700 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A16" id="1063">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1063"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A17" id="1064">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1064"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A18" id="1065">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1065"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A19" id="1066">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1066"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A20" id="1067">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1067"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A21" id="1068">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1068"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A22" id="1069">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1069"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A23" id="1070">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1070"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -5143,6 +6155,42 @@
         <v>37</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="1"/>
+      <c r="B20" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1"/>
+      <c r="B21" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1"/>
+      <c r="B22" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1"/>
+      <c r="B23" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
   <drawing r:id="rId1"/>
@@ -5152,7 +6200,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1044" r:id="rId727" name="A1">
+            <control shapeId="1048" r:id="rId877" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5174,7 +6222,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1045" r:id="rId728" name="A2">
+            <control shapeId="1049" r:id="rId878" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5196,7 +6244,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1046" r:id="rId729" name="A3">
+            <control shapeId="1050" r:id="rId879" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5218,7 +6266,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1047" r:id="rId730" name="A4">
+            <control shapeId="1051" r:id="rId880" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5240,7 +6288,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1048" r:id="rId731" name="A5">
+            <control shapeId="1052" r:id="rId881" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5262,7 +6310,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1049" r:id="rId732" name="A6">
+            <control shapeId="1053" r:id="rId882" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5284,7 +6332,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1050" r:id="rId733" name="A7">
+            <control shapeId="1054" r:id="rId883" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5306,7 +6354,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1051" r:id="rId734" name="A8">
+            <control shapeId="1055" r:id="rId884" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5328,7 +6376,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1052" r:id="rId735" name="A9">
+            <control shapeId="1056" r:id="rId885" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5350,7 +6398,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1053" r:id="rId736" name="A10">
+            <control shapeId="1057" r:id="rId886" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5372,7 +6420,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1054" r:id="rId737" name="A11">
+            <control shapeId="1058" r:id="rId887" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5394,7 +6442,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1055" r:id="rId738" name="A12">
+            <control shapeId="1059" r:id="rId888" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5416,7 +6464,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId739" name="A13">
+            <control shapeId="1060" r:id="rId889" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5438,7 +6486,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId740" name="A14">
+            <control shapeId="1061" r:id="rId890" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5460,7 +6508,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId741" name="A15">
+            <control shapeId="1062" r:id="rId891" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5482,7 +6530,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId742" name="A16">
+            <control shapeId="1063" r:id="rId892" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5504,7 +6552,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId743" name="A17">
+            <control shapeId="1064" r:id="rId893" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5526,7 +6574,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId744" name="A18">
+            <control shapeId="1065" r:id="rId894" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5548,7 +6596,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId745" name="A19">
+            <control shapeId="1066" r:id="rId895" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5568,6 +6616,94 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1067" r:id="rId896" name="A20">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1068" r:id="rId897" name="A21">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1069" r:id="rId898" name="A22">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1070" r:id="rId899" name="A23">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Korean.xlsx
+++ b/AAAGameData/Languages/Korean.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>NoSaveData</t>
   </si>
@@ -87,16 +87,58 @@
     <t>저장 목록 열기</t>
   </si>
   <si>
+    <t>scene.abyss.name</t>
+  </si>
+  <si>
+    <t>심연의 땅</t>
+  </si>
+  <si>
+    <t>scene.avalon.name</t>
+  </si>
+  <si>
+    <t>아발론</t>
+  </si>
+  <si>
+    <t>scene.babylon.name</t>
+  </si>
+  <si>
+    <t>바빌론 공중정원</t>
+  </si>
+  <si>
     <t>scene.base.name</t>
   </si>
   <si>
     <t>기지</t>
   </si>
   <si>
+    <t>scene.herheim.name</t>
+  </si>
+  <si>
+    <t>헤르헤머</t>
+  </si>
+  <si>
     <t>scene.menu.name</t>
   </si>
   <si>
     <t>메인 메뉴</t>
+  </si>
+  <si>
+    <t>scene.olympus.name</t>
+  </si>
+  <si>
+    <t>올림푸스 산</t>
+  </si>
+  <si>
+    <t>scene.takamahara.name</t>
+  </si>
+  <si>
+    <t>고천원</t>
+  </si>
+  <si>
+    <t>scene.tiangong.name</t>
+  </si>
+  <si>
+    <t>천궁</t>
   </si>
   <si>
     <t>scene.tutorial.name</t>
@@ -244,7 +286,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
@@ -252,15 +294,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -276,7 +318,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
@@ -288,7 +330,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
@@ -296,14 +338,42 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -316,15 +386,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
@@ -333,6 +403,338 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -4010,609 +4412,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1048">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1048"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1049">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1049"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1050">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1050"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1051">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1051"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1052">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1052"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1053">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1053"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1054">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1054"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1055">
+            <xdr:cNvPr hidden="1" name="A1" id="1055">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1055"/>
@@ -4687,18 +4487,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1056">
+            <xdr:cNvPr hidden="1" name="A2" id="1056">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1056"/>
@@ -4773,18 +4573,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1057">
+            <xdr:cNvPr hidden="1" name="A3" id="1057">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1057"/>
@@ -4859,18 +4659,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1058">
+            <xdr:cNvPr hidden="1" name="A4" id="1058">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1058"/>
@@ -4945,18 +4745,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1059">
+            <xdr:cNvPr hidden="1" name="A5" id="1059">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1059"/>
@@ -5031,18 +4831,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1060">
+            <xdr:cNvPr hidden="1" name="A6" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1060"/>
@@ -5117,18 +4917,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1061">
+            <xdr:cNvPr hidden="1" name="A7" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -5203,18 +5003,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1062">
+            <xdr:cNvPr hidden="1" name="A8" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1062"/>
@@ -5289,18 +5089,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1063">
+            <xdr:cNvPr hidden="1" name="A9" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1063"/>
@@ -5375,18 +5175,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1064">
+            <xdr:cNvPr hidden="1" name="A10" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1064"/>
@@ -5461,18 +5261,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1065">
+            <xdr:cNvPr hidden="1" name="A11" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1065"/>
@@ -5547,18 +5347,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1066">
+            <xdr:cNvPr hidden="1" name="A12" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1066"/>
@@ -5633,18 +5433,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1067">
+            <xdr:cNvPr hidden="1" name="A13" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1067"/>
@@ -5719,18 +5519,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1068">
+            <xdr:cNvPr hidden="1" name="A14" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1068"/>
@@ -5805,18 +5605,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1069">
+            <xdr:cNvPr hidden="1" name="A15" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1069"/>
@@ -5891,18 +5691,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1070">
+            <xdr:cNvPr hidden="1" name="A16" id="1070">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1070"/>
@@ -5971,16 +5771,1220 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A17" id="1071">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1071"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A18" id="1072">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1072"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A19" id="1073">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1073"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A20" id="1074">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1074"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A21" id="1075">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1075"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A22" id="1076">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1076"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A23" id="1077">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1077"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A24" id="1078">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1078"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A25" id="1079">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1079"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A26" id="1080">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1080"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A27" id="1081">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1081"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A28" id="1082">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1082"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A29" id="1083">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1083"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A30" id="1084">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1084"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22.2728118896484" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6191,6 +7195,69 @@
         <v>45</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="1"/>
+      <c r="B24" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1"/>
+      <c r="B26" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1"/>
+      <c r="B27" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1"/>
+      <c r="B28" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1"/>
+      <c r="B29" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1"/>
+      <c r="B30" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
   <drawing r:id="rId1"/>
@@ -6200,7 +7267,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1048" r:id="rId877" name="A1">
+            <control shapeId="1055" r:id="rId957" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6222,7 +7289,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1049" r:id="rId878" name="A2">
+            <control shapeId="1056" r:id="rId958" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6244,7 +7311,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1050" r:id="rId879" name="A3">
+            <control shapeId="1057" r:id="rId959" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6266,7 +7333,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1051" r:id="rId880" name="A4">
+            <control shapeId="1058" r:id="rId960" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6288,7 +7355,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1052" r:id="rId881" name="A5">
+            <control shapeId="1059" r:id="rId961" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6310,7 +7377,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1053" r:id="rId882" name="A6">
+            <control shapeId="1060" r:id="rId962" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6332,7 +7399,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1054" r:id="rId883" name="A7">
+            <control shapeId="1061" r:id="rId963" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6354,7 +7421,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1055" r:id="rId884" name="A8">
+            <control shapeId="1062" r:id="rId964" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6376,7 +7443,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId885" name="A9">
+            <control shapeId="1063" r:id="rId965" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6398,7 +7465,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId886" name="A10">
+            <control shapeId="1064" r:id="rId966" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6420,7 +7487,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId887" name="A11">
+            <control shapeId="1065" r:id="rId967" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6442,7 +7509,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId888" name="A12">
+            <control shapeId="1066" r:id="rId968" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6464,7 +7531,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId889" name="A13">
+            <control shapeId="1067" r:id="rId969" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6486,7 +7553,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId890" name="A14">
+            <control shapeId="1068" r:id="rId970" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6508,7 +7575,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId891" name="A15">
+            <control shapeId="1069" r:id="rId971" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6530,7 +7597,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId892" name="A16">
+            <control shapeId="1070" r:id="rId972" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6552,7 +7619,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId893" name="A17">
+            <control shapeId="1071" r:id="rId973" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6574,7 +7641,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId894" name="A18">
+            <control shapeId="1072" r:id="rId974" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6596,7 +7663,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId895" name="A19">
+            <control shapeId="1073" r:id="rId975" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6618,7 +7685,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId896" name="A20">
+            <control shapeId="1074" r:id="rId976" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6640,7 +7707,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId897" name="A21">
+            <control shapeId="1075" r:id="rId977" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6662,7 +7729,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId898" name="A22">
+            <control shapeId="1076" r:id="rId978" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6684,7 +7751,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId899" name="A23">
+            <control shapeId="1077" r:id="rId979" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6704,6 +7771,160 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1078" r:id="rId980" name="A24">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1079" r:id="rId981" name="A25">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1080" r:id="rId982" name="A26">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1081" r:id="rId983" name="A27">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1082" r:id="rId984" name="A28">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1083" r:id="rId985" name="A29">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1084" r:id="rId986" name="A30">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>30</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>
